--- a/Lectures/MIP-SpecialEvent.xlsx
+++ b/Lectures/MIP-SpecialEvent.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\Box\_Rosenberg2024\Classes\CEE6410\Fall2024\CEE6410-Rosenberg-GitHub\CEE-6410-Rosenberg\Lectures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0269A442-B994-4521-ACA9-312F9948E92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46E99F39-B840-48C3-96BF-CB439EE90686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6CF1F9DA-B141-4212-A39C-1E996261F1AA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A7D1006E-9CBC-425F-A1EC-6419AA097ED0}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of Contents" sheetId="10" r:id="rId1"/>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA222592-EFDD-4A8A-858B-EEC7A97ADEF9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F038DE68-237B-4CDD-B982-C12647CCA920}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -762,23 +762,23 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" location="Scalar!A1" display="Attendees" xr:uid="{63BCF931-0198-4102-ADBE-4E383AB1E66B}"/>
-    <hyperlink ref="A3" location="Cost!A1" display="Cost" xr:uid="{F37AA292-260D-4103-B778-7BD503D76AF9}"/>
-    <hyperlink ref="A4" location="Scalar!A1" display="MaxAverageTime" xr:uid="{BABF1B84-F379-4FBB-ACC3-BAB914C08632}"/>
-    <hyperlink ref="A5" location="MaxPassengers!A1" display="MaxPassengers" xr:uid="{1BCA0E5E-02E0-40F9-ABF7-AAA579FDE298}"/>
-    <hyperlink ref="A6" location="parklot!A1" display="parklot" xr:uid="{8360692C-0625-414C-9DFF-41A6486C719E}"/>
-    <hyperlink ref="A7" location="ReservationCost!A1" display="ReservationCost" xr:uid="{F26F952A-00C5-4425-A09E-53FD45381114}"/>
-    <hyperlink ref="A8" location="Seats!A1" display="Seats" xr:uid="{70B6AF71-F0C0-4B2F-9034-C7E3E95FB022}"/>
-    <hyperlink ref="A9" location="TravelTime!A1" display="TravelTime" xr:uid="{F1F1552D-4E02-4B56-8E8B-B9BF0D415950}"/>
-    <hyperlink ref="A10" location="UnitCost!A1" display="UnitCost" xr:uid="{62739DB7-A95E-4430-840C-F34DCB7E611B}"/>
-    <hyperlink ref="A11" location="vendor!A1" display="vendor" xr:uid="{ECAD1929-0EF9-409A-833E-713D264F3440}"/>
+    <hyperlink ref="A2" location="Scalar!A1" display="Attendees" xr:uid="{4909F976-9109-4618-908E-F619E34B8DB3}"/>
+    <hyperlink ref="A3" location="Cost!A1" display="Cost" xr:uid="{20A57931-456F-451D-828B-0AFC863B8D59}"/>
+    <hyperlink ref="A4" location="Scalar!A1" display="MaxAverageTime" xr:uid="{728DC529-69D4-4B45-B3AB-C9CD093C6E2B}"/>
+    <hyperlink ref="A5" location="MaxPassengers!A1" display="MaxPassengers" xr:uid="{A95E02BD-8211-4628-9C29-8C183D1F269F}"/>
+    <hyperlink ref="A6" location="parklot!A1" display="parklot" xr:uid="{0DF1F631-0393-446A-B0E3-539681EEDF53}"/>
+    <hyperlink ref="A7" location="ReservationCost!A1" display="ReservationCost" xr:uid="{5B2EA518-AEB0-4BBF-91FA-515164B99D4C}"/>
+    <hyperlink ref="A8" location="Seats!A1" display="Seats" xr:uid="{E2D120C9-34A2-490A-BCA6-21A983C433D7}"/>
+    <hyperlink ref="A9" location="TravelTime!A1" display="TravelTime" xr:uid="{036884EE-08A2-4109-989F-AD6452AA5011}"/>
+    <hyperlink ref="A10" location="UnitCost!A1" display="UnitCost" xr:uid="{A141539F-6393-457F-B6EA-63D245769F51}"/>
+    <hyperlink ref="A11" location="vendor!A1" display="vendor" xr:uid="{1ECCC63B-AE65-4147-AFBD-986F42FD0152}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9BDE91C-E9F5-44A1-9224-4E6036B27D96}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66F54B95-8231-42EE-8FD1-837B74383D34}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -817,16 +817,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:A5" xr:uid="{D9BDE91C-E9F5-44A1-9224-4E6036B27D96}"/>
+  <autoFilter ref="A3:A5" xr:uid="{66F54B95-8231-42EE-8FD1-837B74383D34}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{B99E93B7-75F5-42C6-8034-9C39C0C83447}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{E6F3F094-DA7B-4105-B346-DE2DCF366D57}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8E049A6-4168-4EFC-A4FF-8D81D6ED693C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F10831F7-5672-4CA3-AF64-27EB35D3E622}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -910,14 +910,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{7F31765E-C3AC-4CFD-A659-C5B6F6387007}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{C75950E4-619C-4414-A77F-2AE19772F1D5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BD23A5A-F6BE-4D39-A673-C4E5DCE3756B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43770B73-D591-4C0D-9741-D60157FC122F}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -973,16 +973,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B6" xr:uid="{1BD23A5A-F6BE-4D39-A673-C4E5DCE3756B}"/>
+  <autoFilter ref="A3:B6" xr:uid="{43770B73-D591-4C0D-9741-D60157FC122F}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{ED131F2C-7063-47D1-82F3-714902475389}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{5621938C-3AC8-40F1-A8E3-8C0A61027AD3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE01687-A915-48E0-8B6D-78EDF540F04A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{708C0E03-0536-4A50-A627-DB6BDA938B32}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1038,16 +1038,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B6" xr:uid="{DDE01687-A915-48E0-8B6D-78EDF540F04A}"/>
+  <autoFilter ref="A3:B6" xr:uid="{708C0E03-0536-4A50-A627-DB6BDA938B32}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{7EF2C3C4-B1E2-4428-A757-C08A7C544BF9}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{DEA37231-E0E7-4E89-8C43-2C5539205406}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE158A3-DAD0-4402-8E1A-5D2733EA0691}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D7C1649-84D6-4EEB-AC5E-05DC93E256BE}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1091,16 +1091,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:A6" xr:uid="{9EE158A3-DAD0-4402-8E1A-5D2733EA0691}"/>
+  <autoFilter ref="A3:A6" xr:uid="{8D7C1649-84D6-4EEB-AC5E-05DC93E256BE}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{04B662E8-14E6-44C8-899A-6F704A424434}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{F76363EE-558F-4B7C-8C57-01FEEB3050A7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1545B88B-8FB7-4C6C-A97A-B2FBA4A22C9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E33EA54-954B-4509-8FF8-F19D8D9BC1C1}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1148,16 +1148,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B5" xr:uid="{1545B88B-8FB7-4C6C-A97A-B2FBA4A22C9E}"/>
+  <autoFilter ref="A3:B5" xr:uid="{2E33EA54-954B-4509-8FF8-F19D8D9BC1C1}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{50243BC2-8E0F-4587-BFBB-75090528988E}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{37521021-9B2E-40E7-BAD0-35B798CB6489}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E935F9-0ECA-430F-ABD3-7E71D76F79D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0B7E7E-E053-4FD6-8BAB-93E49049DA5C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1205,16 +1205,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B5" xr:uid="{F6E935F9-0ECA-430F-ABD3-7E71D76F79D8}"/>
+  <autoFilter ref="A3:B5" xr:uid="{7E0B7E7E-E053-4FD6-8BAB-93E49049DA5C}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{3AE6159C-C899-4125-9693-D34B2EF19596}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{CF7156A4-5063-4FBC-A219-C94CCBB6E8F3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58E383B7-BF10-4B65-95FB-9B626B485EEF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D39AD1C6-0AFE-41FD-903C-1B6E9D8F28D9}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1270,16 +1270,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B6" xr:uid="{58E383B7-BF10-4B65-95FB-9B626B485EEF}"/>
+  <autoFilter ref="A3:B6" xr:uid="{D39AD1C6-0AFE-41FD-903C-1B6E9D8F28D9}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{4D7BFCEF-3F8D-41EE-B509-4E89AEC9B042}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{AD6B4CA9-B0FF-4777-A491-6995B9DA064E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EC6B997-8B23-4625-8394-1FAD4F20B37A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC7819A2-D160-4508-8930-F8D80CCA5683}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1327,9 +1327,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B5" xr:uid="{7EC6B997-8B23-4625-8394-1FAD4F20B37A}"/>
+  <autoFilter ref="A3:B5" xr:uid="{AC7819A2-D160-4508-8930-F8D80CCA5683}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{2FC89E8B-80A9-4E1B-9A3A-2AA9F9400142}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{D216D151-F9D4-49AF-9D73-B4E9632FE124}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Lectures/MIP-SpecialEvent.xlsx
+++ b/Lectures/MIP-SpecialEvent.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\Box\_Rosenberg2024\Classes\CEE6410\Fall2024\CEE6410-Rosenberg-GitHub\CEE-6410-Rosenberg\Lectures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46E99F39-B840-48C3-96BF-CB439EE90686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B71BDC6F-0D11-41BB-98D8-ED5FE79AA7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A7D1006E-9CBC-425F-A1EC-6419AA097ED0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0C2B917E-702B-4174-9CDB-DA9B6AC0EBDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of Contents" sheetId="10" r:id="rId1"/>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F038DE68-237B-4CDD-B982-C12647CCA920}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CDBCC67-981A-4AEF-BDD2-EAB9AF1A9B68}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -762,23 +762,23 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" location="Scalar!A1" display="Attendees" xr:uid="{4909F976-9109-4618-908E-F619E34B8DB3}"/>
-    <hyperlink ref="A3" location="Cost!A1" display="Cost" xr:uid="{20A57931-456F-451D-828B-0AFC863B8D59}"/>
-    <hyperlink ref="A4" location="Scalar!A1" display="MaxAverageTime" xr:uid="{728DC529-69D4-4B45-B3AB-C9CD093C6E2B}"/>
-    <hyperlink ref="A5" location="MaxPassengers!A1" display="MaxPassengers" xr:uid="{A95E02BD-8211-4628-9C29-8C183D1F269F}"/>
-    <hyperlink ref="A6" location="parklot!A1" display="parklot" xr:uid="{0DF1F631-0393-446A-B0E3-539681EEDF53}"/>
-    <hyperlink ref="A7" location="ReservationCost!A1" display="ReservationCost" xr:uid="{5B2EA518-AEB0-4BBF-91FA-515164B99D4C}"/>
-    <hyperlink ref="A8" location="Seats!A1" display="Seats" xr:uid="{E2D120C9-34A2-490A-BCA6-21A983C433D7}"/>
-    <hyperlink ref="A9" location="TravelTime!A1" display="TravelTime" xr:uid="{036884EE-08A2-4109-989F-AD6452AA5011}"/>
-    <hyperlink ref="A10" location="UnitCost!A1" display="UnitCost" xr:uid="{A141539F-6393-457F-B6EA-63D245769F51}"/>
-    <hyperlink ref="A11" location="vendor!A1" display="vendor" xr:uid="{1ECCC63B-AE65-4147-AFBD-986F42FD0152}"/>
+    <hyperlink ref="A2" location="Scalar!A1" display="Attendees" xr:uid="{285464EF-F305-4FD5-8914-71E119F411AF}"/>
+    <hyperlink ref="A3" location="Cost!A1" display="Cost" xr:uid="{C789CCF5-9195-45B3-8ACF-CD38BDF37660}"/>
+    <hyperlink ref="A4" location="Scalar!A1" display="MaxAverageTime" xr:uid="{4E6888A9-05E6-472E-AF3E-38C34029324C}"/>
+    <hyperlink ref="A5" location="MaxPassengers!A1" display="MaxPassengers" xr:uid="{E7965824-733C-4B2A-B98D-C6533B6BCEF0}"/>
+    <hyperlink ref="A6" location="parklot!A1" display="parklot" xr:uid="{5D8BDA1A-67D4-4B4C-8F81-654083D113B6}"/>
+    <hyperlink ref="A7" location="ReservationCost!A1" display="ReservationCost" xr:uid="{D227E78A-F696-47A4-8B03-EE9C3DDE9DFA}"/>
+    <hyperlink ref="A8" location="Seats!A1" display="Seats" xr:uid="{E0B413BA-A18A-44A1-846D-B8742FD87807}"/>
+    <hyperlink ref="A9" location="TravelTime!A1" display="TravelTime" xr:uid="{678C3619-84EC-401A-B787-6E4A1955E75C}"/>
+    <hyperlink ref="A10" location="UnitCost!A1" display="UnitCost" xr:uid="{42787E9C-10FC-423F-A998-05CB0BEC6694}"/>
+    <hyperlink ref="A11" location="vendor!A1" display="vendor" xr:uid="{F4DE0099-BC75-40EB-BC81-35B760ACA762}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66F54B95-8231-42EE-8FD1-837B74383D34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2FE5CA0-DAAF-431B-A34D-F1B5B17C9137}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -817,16 +817,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:A5" xr:uid="{66F54B95-8231-42EE-8FD1-837B74383D34}"/>
+  <autoFilter ref="A3:A5" xr:uid="{B2FE5CA0-DAAF-431B-A34D-F1B5B17C9137}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{E6F3F094-DA7B-4105-B346-DE2DCF366D57}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{3F7906BC-05FF-4581-94F5-EEDCE79A3A26}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F10831F7-5672-4CA3-AF64-27EB35D3E622}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62D9C923-D92E-4C79-A8F7-9852082FD389}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -910,14 +910,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{C75950E4-619C-4414-A77F-2AE19772F1D5}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{4958DB77-AE80-49B3-A000-7E3562E88E52}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43770B73-D591-4C0D-9741-D60157FC122F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86EA260A-404E-4699-AE9C-2019EE1715C3}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -973,16 +973,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B6" xr:uid="{43770B73-D591-4C0D-9741-D60157FC122F}"/>
+  <autoFilter ref="A3:B6" xr:uid="{86EA260A-404E-4699-AE9C-2019EE1715C3}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{5621938C-3AC8-40F1-A8E3-8C0A61027AD3}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{C41E7030-A574-4307-940C-9A9F58940BD3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{708C0E03-0536-4A50-A627-DB6BDA938B32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79DAE38B-CC13-4947-A121-65571EAD812B}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1038,16 +1038,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B6" xr:uid="{708C0E03-0536-4A50-A627-DB6BDA938B32}"/>
+  <autoFilter ref="A3:B6" xr:uid="{79DAE38B-CC13-4947-A121-65571EAD812B}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{DEA37231-E0E7-4E89-8C43-2C5539205406}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{A584189E-69CE-415F-86E8-DB72F40B8299}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D7C1649-84D6-4EEB-AC5E-05DC93E256BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C021D0D3-008D-42D5-A761-D60A9FA74781}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1091,16 +1091,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:A6" xr:uid="{8D7C1649-84D6-4EEB-AC5E-05DC93E256BE}"/>
+  <autoFilter ref="A3:A6" xr:uid="{C021D0D3-008D-42D5-A761-D60A9FA74781}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{F76363EE-558F-4B7C-8C57-01FEEB3050A7}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{0C51D854-D001-4845-9E4E-45BFCDDAEAF5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E33EA54-954B-4509-8FF8-F19D8D9BC1C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2792F8F1-B91C-4141-8EEC-AD93683033F1}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1148,16 +1148,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B5" xr:uid="{2E33EA54-954B-4509-8FF8-F19D8D9BC1C1}"/>
+  <autoFilter ref="A3:B5" xr:uid="{2792F8F1-B91C-4141-8EEC-AD93683033F1}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{37521021-9B2E-40E7-BAD0-35B798CB6489}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{70EE90A4-DF89-44B4-B6FA-1094F2065F7E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0B7E7E-E053-4FD6-8BAB-93E49049DA5C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BBF91F-DD47-4C13-B391-D1201541968A}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1205,16 +1205,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B5" xr:uid="{7E0B7E7E-E053-4FD6-8BAB-93E49049DA5C}"/>
+  <autoFilter ref="A3:B5" xr:uid="{F0BBF91F-DD47-4C13-B391-D1201541968A}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{CF7156A4-5063-4FBC-A219-C94CCBB6E8F3}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{EEF0FA88-4238-48AB-A24C-530FDE434849}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D39AD1C6-0AFE-41FD-903C-1B6E9D8F28D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91ADB9DE-1D8E-4136-A973-E444904E7C9B}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1270,16 +1270,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B6" xr:uid="{D39AD1C6-0AFE-41FD-903C-1B6E9D8F28D9}"/>
+  <autoFilter ref="A3:B6" xr:uid="{91ADB9DE-1D8E-4136-A973-E444904E7C9B}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{AD6B4CA9-B0FF-4777-A491-6995B9DA064E}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{071DC89E-E963-4CEB-BCB4-E942D0C0D476}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC7819A2-D160-4508-8930-F8D80CCA5683}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A8E45F-90EF-4EEE-8C45-EB93007CA873}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1327,9 +1327,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B5" xr:uid="{AC7819A2-D160-4508-8930-F8D80CCA5683}"/>
+  <autoFilter ref="A3:B5" xr:uid="{06A8E45F-90EF-4EEE-8C45-EB93007CA873}"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{D216D151-F9D4-49AF-9D73-B4E9632FE124}"/>
+    <hyperlink ref="A1" location="'Table of Contents'!A1" display="TOC" xr:uid="{883F451A-807B-4F92-A776-3567297AFBF7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
